--- a/jogos_2025-07-09.xlsx
+++ b/jogos_2025-07-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -184,21 +184,27 @@
     <t>DateTime</t>
   </si>
   <si>
+    <t>20:00</t>
+  </si>
+  <si>
     <t>20:30</t>
   </si>
   <si>
     <t>23:30</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>USA MLS</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
+    <t>Crown Legacy</t>
+  </si>
+  <si>
     <t>New England Revolution</t>
   </si>
   <si>
@@ -206,6 +212,9 @@
   </si>
   <si>
     <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
   </si>
   <si>
     <t>Inter Miami</t>
@@ -584,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:BD5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -765,16 +774,16 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -789,94 +798,94 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L2">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AK2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AL2">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <v>-1</v>
@@ -918,13 +927,13 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BC2">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD2" s="3">
-        <v>45847.85416666666</v>
+        <v>45847.83333333334</v>
       </c>
     </row>
     <row r="3" spans="1:56">
@@ -932,19 +941,19 @@
         <v>45847</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -959,127 +968,127 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AK3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1088,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD3" s="3">
         <v>45847.85416666666</v>
@@ -1105,16 +1114,16 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1129,94 +1138,94 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L4">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>17.25</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AK4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AL4">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1258,12 +1267,182 @@
         <v>0</v>
       </c>
       <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="3">
+        <v>45847.85416666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:56">
+      <c r="A5" s="2">
+        <v>45847</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5">
+        <v>1.29</v>
+      </c>
+      <c r="M5">
+        <v>4.8</v>
+      </c>
+      <c r="N5">
+        <v>7.3</v>
+      </c>
+      <c r="O5">
         <v>1.53</v>
       </c>
-      <c r="BC4">
+      <c r="P5">
+        <v>17.25</v>
+      </c>
+      <c r="Q5">
         <v>2.5</v>
       </c>
-      <c r="BD4" s="3">
+      <c r="R5">
+        <v>1.3</v>
+      </c>
+      <c r="S5">
+        <v>3.4</v>
+      </c>
+      <c r="T5">
+        <v>2.5</v>
+      </c>
+      <c r="U5">
+        <v>1.5</v>
+      </c>
+      <c r="V5">
+        <v>6</v>
+      </c>
+      <c r="W5">
+        <v>1.13</v>
+      </c>
+      <c r="X5">
+        <v>1.04</v>
+      </c>
+      <c r="Y5">
+        <v>10</v>
+      </c>
+      <c r="Z5">
+        <v>1.14</v>
+      </c>
+      <c r="AA5">
+        <v>4.4</v>
+      </c>
+      <c r="AB5">
+        <v>1.57</v>
+      </c>
+      <c r="AC5">
+        <v>2.25</v>
+      </c>
+      <c r="AD5">
+        <v>2.25</v>
+      </c>
+      <c r="AE5">
+        <v>1.57</v>
+      </c>
+      <c r="AF5">
+        <v>1.62</v>
+      </c>
+      <c r="AG5">
+        <v>2.2</v>
+      </c>
+      <c r="AH5">
+        <v>4.1</v>
+      </c>
+      <c r="AI5">
+        <v>1.18</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AL5">
+        <v>1.08</v>
+      </c>
+      <c r="AM5">
+        <v>1.17</v>
+      </c>
+      <c r="AN5">
+        <v>3.08</v>
+      </c>
+      <c r="AO5">
+        <v>-1</v>
+      </c>
+      <c r="AP5">
+        <v>1.26</v>
+      </c>
+      <c r="AQ5">
+        <v>1.47</v>
+      </c>
+      <c r="AR5">
+        <v>1.76</v>
+      </c>
+      <c r="AS5">
+        <v>2.18</v>
+      </c>
+      <c r="AT5">
+        <v>2.8</v>
+      </c>
+      <c r="AU5">
+        <v>3.4</v>
+      </c>
+      <c r="AV5">
+        <v>2.48</v>
+      </c>
+      <c r="AW5">
+        <v>1.94</v>
+      </c>
+      <c r="AX5">
+        <v>1.58</v>
+      </c>
+      <c r="AY5">
+        <v>1.36</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>1.53</v>
+      </c>
+      <c r="BC5">
+        <v>2.5</v>
+      </c>
+      <c r="BD5" s="3">
         <v>45847.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-09.xlsx
+++ b/jogos_2025-07-09.xlsx
@@ -205,22 +205,22 @@
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
     <t>New England Revolution</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>FC Cincinnati II</t>
+  </si>
+  <si>
     <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>FC Cincinnati II</t>
   </si>
   <si>
     <t>Colorado Rapids</t>
@@ -944,7 +944,7 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
         <v>61</v>
@@ -971,76 +971,76 @@
         <v>70</v>
       </c>
       <c r="L3">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="s">
         <v>71</v>
@@ -1049,46 +1049,46 @@
         <v>71</v>
       </c>
       <c r="AL3">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR3">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS3">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT3">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU3">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV3">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW3">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX3">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY3">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BC3">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD3" s="3">
         <v>45847.85416666666</v>
@@ -1114,7 +1114,7 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
@@ -1141,76 +1141,76 @@
         <v>70</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ4" t="s">
         <v>71</v>
@@ -1219,46 +1219,46 @@
         <v>71</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD4" s="3">
         <v>45847.85416666666</v>
@@ -1365,10 +1365,10 @@
         <v>2.25</v>
       </c>
       <c r="AD5">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE5">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AF5">
         <v>1.62</v>

--- a/jogos_2025-07-09.xlsx
+++ b/jogos_2025-07-09.xlsx
@@ -205,22 +205,22 @@
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
     <t>FC Cincinnati II</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
   </si>
   <si>
     <t>Colorado Rapids</t>
@@ -801,76 +801,76 @@
         <v>70</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AJ2" t="s">
         <v>71</v>
@@ -879,13 +879,13 @@
         <v>71</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO2">
         <v>-1</v>
@@ -927,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD2" s="3">
         <v>45847.83333333334</v>
@@ -944,7 +944,7 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
         <v>61</v>
@@ -971,76 +971,76 @@
         <v>70</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ3" t="s">
         <v>71</v>
@@ -1049,46 +1049,46 @@
         <v>71</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD3" s="3">
         <v>45847.85416666666</v>
@@ -1114,7 +1114,7 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
@@ -1141,37 +1141,37 @@
         <v>70</v>
       </c>
       <c r="L4">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="M4">
-        <v>3.47</v>
+        <v>4.28</v>
       </c>
       <c r="N4">
-        <v>2.42</v>
+        <v>3.67</v>
       </c>
       <c r="O4">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="P4">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Q4">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="T4">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V4">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>1.13</v>
@@ -1183,34 +1183,34 @@
         <v>17</v>
       </c>
       <c r="Z4">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AA4">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AB4">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AC4">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="AD4">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AE4">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF4">
         <v>1.45</v>
       </c>
       <c r="AG4">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH4">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AI4">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AJ4" t="s">
         <v>71</v>
@@ -1219,58 +1219,58 @@
         <v>71</v>
       </c>
       <c r="AL4">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AM4">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AN4">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR4">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS4">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>1.5</v>
+      </c>
+      <c r="BC4">
         <v>2.6</v>
-      </c>
-      <c r="AU4">
-        <v>3.65</v>
-      </c>
-      <c r="AV4">
-        <v>2.65</v>
-      </c>
-      <c r="AW4">
-        <v>2.04</v>
-      </c>
-      <c r="AX4">
-        <v>1.66</v>
-      </c>
-      <c r="AY4">
-        <v>1.43</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.04</v>
-      </c>
-      <c r="BC4">
-        <v>1.83</v>
       </c>
       <c r="BD4" s="3">
         <v>45847.85416666666</v>
@@ -1359,10 +1359,10 @@
         <v>4.4</v>
       </c>
       <c r="AB5">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AC5">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AD5">
         <v>2.2</v>

--- a/jogos_2025-07-09.xlsx
+++ b/jogos_2025-07-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>Date</t>
   </si>
@@ -125,60 +125,6 @@
   </si>
   <si>
     <t>awayGoals</t>
-  </si>
-  <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
   </si>
   <si>
     <t>DateTime</t>
@@ -593,10 +539,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD5"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,79 +657,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45847</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -798,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L2">
         <v>3.8</v>
@@ -873,87 +765,33 @@
         <v>1.19</v>
       </c>
       <c r="AJ2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="AK2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL2">
-        <v>1.16</v>
-      </c>
-      <c r="AM2">
-        <v>1.21</v>
-      </c>
-      <c r="AN2">
-        <v>1.3</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>2.6</v>
-      </c>
-      <c r="BC2">
-        <v>1.5</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>53</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45847.83333333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45847</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -968,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L3">
         <v>2.39</v>
@@ -1043,87 +881,33 @@
         <v>1.21</v>
       </c>
       <c r="AJ3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="AK3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL3">
-        <v>1.6</v>
-      </c>
-      <c r="AM3">
-        <v>1.28</v>
-      </c>
-      <c r="AN3">
-        <v>1.44</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.23</v>
-      </c>
-      <c r="AQ3">
-        <v>1.41</v>
-      </c>
-      <c r="AR3">
-        <v>1.68</v>
-      </c>
-      <c r="AS3">
-        <v>2.06</v>
-      </c>
-      <c r="AT3">
-        <v>2.6</v>
-      </c>
-      <c r="AU3">
-        <v>3.65</v>
-      </c>
-      <c r="AV3">
-        <v>2.65</v>
-      </c>
-      <c r="AW3">
-        <v>2.04</v>
-      </c>
-      <c r="AX3">
-        <v>1.66</v>
-      </c>
-      <c r="AY3">
-        <v>1.43</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.04</v>
-      </c>
-      <c r="BC3">
-        <v>1.83</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>53</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45847.85416666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45847</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1138,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L4">
         <v>1.72</v>
@@ -1213,87 +997,33 @@
         <v>1.17</v>
       </c>
       <c r="AJ4" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="AK4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL4">
-        <v>1.14</v>
-      </c>
-      <c r="AM4">
-        <v>1.13</v>
-      </c>
-      <c r="AN4">
-        <v>1.95</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.5</v>
-      </c>
-      <c r="BC4">
-        <v>2.6</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>53</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45847.85416666666</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45847</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1308,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="L5">
         <v>1.29</v>
@@ -1383,66 +1113,12 @@
         <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="AK5" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL5">
-        <v>1.08</v>
-      </c>
-      <c r="AM5">
-        <v>1.17</v>
-      </c>
-      <c r="AN5">
-        <v>3.08</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>1.26</v>
-      </c>
-      <c r="AQ5">
-        <v>1.47</v>
-      </c>
-      <c r="AR5">
-        <v>1.76</v>
-      </c>
-      <c r="AS5">
-        <v>2.18</v>
-      </c>
-      <c r="AT5">
-        <v>2.8</v>
-      </c>
-      <c r="AU5">
-        <v>3.4</v>
-      </c>
-      <c r="AV5">
-        <v>2.48</v>
-      </c>
-      <c r="AW5">
-        <v>1.94</v>
-      </c>
-      <c r="AX5">
-        <v>1.58</v>
-      </c>
-      <c r="AY5">
-        <v>1.36</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.53</v>
-      </c>
-      <c r="BC5">
-        <v>2.5</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>53</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45847.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-09.xlsx
+++ b/jogos_2025-07-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -136,7 +136,7 @@
     <t>20:30</t>
   </si>
   <si>
-    <t>23:30</t>
+    <t>23:25</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
@@ -172,10 +172,19 @@
     <t>Colorado Rapids</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>complete</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
+    <t>['42', '48', '59']</t>
+  </si>
+  <si>
+    <t>['27', '38']</t>
   </si>
 </sst>
 </file>
@@ -711,22 +720,22 @@
         <v>1.5</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
         <v>3.2</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V2">
         <v>4.75</v>
       </c>
       <c r="W2">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X2">
         <v>1</v>
@@ -735,22 +744,22 @@
         <v>12</v>
       </c>
       <c r="Z2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA2">
         <v>4.5</v>
       </c>
       <c r="AB2">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC2">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD2">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF2">
         <v>1.42</v>
@@ -759,10 +768,10 @@
         <v>2.5</v>
       </c>
       <c r="AH2">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="AI2">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AJ2" t="s">
         <v>53</v>
@@ -794,16 +803,16 @@
         <v>49</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="s">
         <v>52</v>
@@ -881,10 +890,10 @@
         <v>1.21</v>
       </c>
       <c r="AJ3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AK3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AL3" s="3">
         <v>45847.85416666666</v>
@@ -925,13 +934,13 @@
         <v>52</v>
       </c>
       <c r="L4">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="M4">
-        <v>4.28</v>
+        <v>4.03</v>
       </c>
       <c r="N4">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="O4">
         <v>1.5</v>
@@ -946,55 +955,55 @@
         <v>1.27</v>
       </c>
       <c r="S4">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="T4">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AA4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB4">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC4">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD4">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="AE4">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AF4">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AG4">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH4">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="AI4">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AJ4" t="s">
         <v>53</v>
@@ -1026,13 +1035,13 @@
         <v>51</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1113,13 +1122,13 @@
         <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="s">
         <v>53</v>
       </c>
       <c r="AL5" s="3">
-        <v>45847.97916666666</v>
+        <v>45847.97569444445</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-07-09.xlsx
+++ b/jogos_2025-07-09.xlsx
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>5.13</v>
+        <v>4.8</v>
       </c>
       <c r="N9" t="n">
-        <v>7.18</v>
+        <v>7.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2.2</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45847.97569444445</v>
